--- a/Excels/Textures.xlsx
+++ b/Excels/Textures.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="13680" windowHeight="4560"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
   <si>
     <t>唯一标识</t>
   </si>
@@ -50,9 +50,6 @@
   </si>
   <si>
     <t>client</t>
-  </si>
-  <si>
-    <t>4pd_img_background_lobby_1</t>
   </si>
 </sst>
 </file>
@@ -1031,12 +1028,7 @@
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="2">
-        <v>1</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="A5" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
